--- a/translations/welsh-translations/11-cso-statement-submit.xlsx
+++ b/translations/welsh-translations/11-cso-statement-submit.xlsx
@@ -686,7 +686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
